--- a/Ingredients Price table Web.xlsx
+++ b/Ingredients Price table Web.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6024AE9A-0376-46ED-925B-EC08573A3C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AF8776-C779-4C0F-BA3F-3145F265FD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69CAB99C-E3EE-4D15-B6BE-5479B7A51CB5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69CAB99C-E3EE-4D15-B6BE-5479B7A51CB5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="311">
   <si>
     <t>Code</t>
   </si>
@@ -969,6 +969,9 @@
   </si>
   <si>
     <t>Felbro</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1098,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1116,28 +1119,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1146,20 +1148,20 @@
     <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1514,2604 +1516,2612 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:6" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="8"/>
+    <row r="3" spans="2:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>310</v>
+      </c>
       <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+      <c r="D3" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="F3" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="19">
         <v>2.35</v>
       </c>
     </row>
-    <row r="5" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="12" t="s">
+    <row r="5" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="19">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
+    <row r="6" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="20"/>
-    </row>
-    <row r="7" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
+      <c r="F6" s="19"/>
+    </row>
+    <row r="7" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="19">
         <v>1.79</v>
       </c>
     </row>
-    <row r="8" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="12" t="s">
+    <row r="8" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="19">
         <v>1.94</v>
       </c>
     </row>
-    <row r="9" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="12" t="s">
+    <row r="9" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="19">
         <v>5.19</v>
       </c>
     </row>
-    <row r="10" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="12" t="s">
+    <row r="10" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="19">
         <v>5.79</v>
       </c>
     </row>
-    <row r="11" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
+    <row r="11" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="19">
         <f>68.49/50</f>
         <v>1.3697999999999999</v>
       </c>
     </row>
-    <row r="12" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="12" t="s">
+    <row r="12" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="19">
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="13" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="12" t="s">
+    <row r="13" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="19">
         <v>1.99</v>
       </c>
     </row>
-    <row r="14" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
+    <row r="14" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="19">
         <v>4.99</v>
       </c>
     </row>
-    <row r="15" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="12" t="s">
+    <row r="15" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="19">
         <f>1674/600</f>
         <v>2.79</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="12" t="s">
+    <row r="16" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="19">
         <v>0.59</v>
       </c>
     </row>
-    <row r="17" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="12"/>
-      <c r="C17" s="12" t="s">
+    <row r="17" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="19">
         <f>86.36/40</f>
         <v>2.1589999999999998</v>
       </c>
     </row>
-    <row r="18" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="12"/>
-      <c r="C18" s="12" t="s">
+    <row r="18" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="19">
         <f>586.89/300</f>
         <v>1.9562999999999999</v>
       </c>
     </row>
-    <row r="19" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="12" t="s">
+    <row r="19" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="20"/>
-    </row>
-    <row r="20" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="12" t="s">
+      <c r="F19" s="19"/>
+    </row>
+    <row r="20" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="19">
         <v>2.25</v>
       </c>
     </row>
-    <row r="21" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
+    <row r="21" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="19">
         <f>2511.34/(26*40)</f>
         <v>2.4147500000000002</v>
       </c>
     </row>
-    <row r="22" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="14" t="s">
+    <row r="22" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="19">
         <f>27/(4.4*4)</f>
         <v>1.5340909090909089</v>
       </c>
     </row>
-    <row r="23" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="21" t="s">
+    <row r="23" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="19">
         <v>2.31</v>
       </c>
     </row>
-    <row r="24" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="21"/>
-      <c r="C24" s="14" t="s">
+    <row r="24" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="23"/>
+      <c r="C24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="19">
         <f>80.31/30</f>
         <v>2.677</v>
       </c>
     </row>
-    <row r="25" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="12" t="s">
+    <row r="25" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B25" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="20"/>
-    </row>
-    <row r="26" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="12" t="s">
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="19"/>
+    </row>
+    <row r="26" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="20"/>
-    </row>
-    <row r="27" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="12" t="s">
+      <c r="E26" s="11"/>
+      <c r="F26" s="19"/>
+    </row>
+    <row r="27" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="20">
+      <c r="F27" s="19">
         <f>829.9/(22*10)</f>
         <v>3.772272727272727</v>
       </c>
     </row>
-    <row r="28" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="12" t="s">
+    <row r="28" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="19">
         <f>49/25</f>
         <v>1.96</v>
       </c>
     </row>
-    <row r="29" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="21" t="s">
+    <row r="29" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="20"/>
-    </row>
-    <row r="30" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="21"/>
-      <c r="C30" s="14" t="s">
+      <c r="F29" s="19"/>
+    </row>
+    <row r="30" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B30" s="23"/>
+      <c r="C30" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="19">
         <f>1256/(6.61387*4*20)</f>
         <v>2.3737993035847396</v>
       </c>
     </row>
-    <row r="31" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="14" t="s">
+    <row r="31" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="20"/>
-    </row>
-    <row r="32" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="14" t="s">
+      <c r="F31" s="19"/>
+    </row>
+    <row r="32" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="20">
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="14" t="s">
+    <row r="33" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="19">
         <v>2.19</v>
       </c>
     </row>
-    <row r="34" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="14" t="s">
+    <row r="34" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B34" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="19">
         <f>1896.49/953.06</f>
         <v>1.9898957043627894</v>
       </c>
     </row>
-    <row r="35" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="12" t="s">
+    <row r="35" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B35" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="19">
         <f>679.3/264.6</f>
         <v>2.5672713529856384</v>
       </c>
     </row>
-    <row r="36" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="12" t="s">
+    <row r="36" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="19">
         <f>192/144</f>
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="37" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="12" t="s">
+    <row r="37" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F37" s="20">
+      <c r="F37" s="19">
         <f>33.78/22.05</f>
         <v>1.5319727891156463</v>
       </c>
     </row>
-    <row r="38" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="12" t="s">
+    <row r="38" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B38" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="19">
         <f>32.24/22.05</f>
         <v>1.4621315192743765</v>
       </c>
     </row>
-    <row r="39" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="12" t="s">
+    <row r="39" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E39" s="12" t="s">
+      <c r="E39" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="19">
         <v>0.9</v>
       </c>
     </row>
-    <row r="40" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="12" t="s">
+    <row r="40" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B40" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F40" s="20">
+      <c r="F40" s="19">
         <v>0.98</v>
       </c>
     </row>
-    <row r="41" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="12" t="s">
+    <row r="41" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B41" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E41" s="12" t="s">
+      <c r="E41" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="20">
+      <c r="F41" s="19">
         <f>460/120</f>
         <v>3.8333333333333335</v>
       </c>
     </row>
-    <row r="42" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="12" t="s">
+    <row r="42" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B42" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12" t="s">
+      <c r="D42" s="11"/>
+      <c r="E42" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F42" s="20">
+      <c r="F42" s="19">
         <f>80/30</f>
         <v>2.6666666666666665</v>
       </c>
     </row>
-    <row r="43" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="14" t="s">
+    <row r="43" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E43" s="12" t="s">
+      <c r="E43" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F43" s="20">
+      <c r="F43" s="19">
         <v>0.89</v>
       </c>
     </row>
-    <row r="44" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="14" t="s">
+    <row r="44" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="C44" s="14" t="s">
+      <c r="C44" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="20">
+      <c r="F44" s="19">
         <v>0.99</v>
       </c>
     </row>
-    <row r="45" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="12" t="s">
+    <row r="45" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="14" t="s">
+      <c r="C45" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F45" s="20">
+      <c r="F45" s="19">
         <f>60.43/38</f>
         <v>1.5902631578947368</v>
       </c>
     </row>
-    <row r="46" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="12" t="s">
+    <row r="46" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B46" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="F46" s="20">
+      <c r="F46" s="19">
         <f>86/76</f>
         <v>1.131578947368421</v>
       </c>
     </row>
-    <row r="47" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="12" t="s">
+    <row r="47" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="12" t="s">
+      <c r="E47" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F47" s="20">
+      <c r="F47" s="19">
         <v>4.99</v>
       </c>
     </row>
-    <row r="48" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="12" t="s">
+    <row r="48" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B48" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F48" s="20">
+      <c r="F48" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="12" t="s">
+    <row r="49" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E49" s="12" t="s">
+      <c r="E49" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="23">
+      <c r="F49" s="21">
         <v>0.99</v>
       </c>
     </row>
-    <row r="50" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="21" t="s">
+    <row r="50" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="F50" s="20">
+      <c r="F50" s="19">
         <v>54.54</v>
       </c>
     </row>
-    <row r="51" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="21"/>
-      <c r="C51" s="12" t="s">
+    <row r="51" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="23"/>
+      <c r="C51" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F51" s="20">
+      <c r="F51" s="19">
         <v>27.44</v>
       </c>
     </row>
-    <row r="52" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B52" s="12" t="s">
+    <row r="52" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B52" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D52" s="15" t="s">
+      <c r="D52" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F52" s="20">
+      <c r="F52" s="19">
         <f>45.25/25</f>
         <v>1.81</v>
       </c>
     </row>
-    <row r="53" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="12" t="s">
+    <row r="53" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B53" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E53" s="12" t="s">
+      <c r="E53" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="20">
+      <c r="F53" s="19">
         <f>690/132</f>
         <v>5.2272727272727275</v>
       </c>
     </row>
-    <row r="54" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="12" t="s">
+    <row r="54" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B54" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F54" s="20">
+      <c r="F54" s="19">
         <v>13.41</v>
       </c>
     </row>
-    <row r="55" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="12" t="s">
+    <row r="55" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B55" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E55" s="12" t="s">
+      <c r="E55" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F55" s="20">
+      <c r="F55" s="19">
         <v>7.19</v>
       </c>
     </row>
-    <row r="56" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="12" t="s">
+    <row r="56" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B56" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="D56" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="20">
+      <c r="F56" s="19">
         <v>6.6</v>
       </c>
     </row>
-    <row r="57" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="12" t="s">
+    <row r="57" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E57" s="12" t="s">
+      <c r="E57" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F57" s="19">
         <f>136.47/20</f>
         <v>6.8235000000000001</v>
       </c>
     </row>
-    <row r="58" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="12" t="s">
+    <row r="58" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B58" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="D58" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="E58" s="12"/>
-      <c r="F58" s="20"/>
-    </row>
-    <row r="59" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="12" t="s">
+      <c r="E58" s="11"/>
+      <c r="F58" s="19"/>
+    </row>
+    <row r="59" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B59" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="E59" s="12" t="s">
+      <c r="E59" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F59" s="20">
+      <c r="F59" s="19">
         <f>60.99/50</f>
         <v>1.2198</v>
       </c>
     </row>
-    <row r="60" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B60" s="14" t="s">
+    <row r="60" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B60" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D60" s="12" t="s">
+      <c r="D60" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="E60" s="12" t="s">
+      <c r="E60" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F60" s="20">
+      <c r="F60" s="19">
         <v>1.05</v>
       </c>
     </row>
-    <row r="61" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="14" t="s">
+    <row r="61" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B61" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="E61" s="12" t="s">
+      <c r="E61" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F61" s="20">
+      <c r="F61" s="19">
         <f>45.95/25</f>
         <v>1.8380000000000001</v>
       </c>
     </row>
-    <row r="62" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="12"/>
-      <c r="C62" s="12" t="s">
+    <row r="62" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="11"/>
+      <c r="C62" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D62" s="12" t="s">
+      <c r="D62" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E62" s="12" t="s">
+      <c r="E62" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F62" s="20">
+      <c r="F62" s="19">
         <f>45.95/50</f>
         <v>0.91900000000000004</v>
       </c>
     </row>
-    <row r="63" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="12" t="s">
+    <row r="63" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D63" s="12" t="s">
+      <c r="D63" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E63" s="12" t="s">
+      <c r="E63" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F63" s="20">
+      <c r="F63" s="19">
         <f>48.16/20</f>
         <v>2.4079999999999999</v>
       </c>
     </row>
-    <row r="64" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="12" t="s">
+    <row r="64" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C64" s="12" t="s">
+      <c r="C64" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="D64" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="E64" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F64" s="20">
+      <c r="F64" s="19">
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="65" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B65" s="12" t="s">
+    <row r="65" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B65" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E65" s="12" t="s">
+      <c r="E65" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F65" s="20">
+      <c r="F65" s="19">
         <v>6.34</v>
       </c>
     </row>
-    <row r="66" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="12" t="s">
+    <row r="66" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B66" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C66" s="12" t="s">
+      <c r="C66" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="E66" s="12" t="s">
+      <c r="E66" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="F66" s="20">
+      <c r="F66" s="19">
         <v>4.8</v>
       </c>
     </row>
-    <row r="67" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="12" t="s">
+    <row r="67" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B67" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D67" s="12" t="s">
+      <c r="D67" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E67" s="12" t="s">
+      <c r="E67" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F67" s="20">
+      <c r="F67" s="19">
         <v>2.68</v>
       </c>
     </row>
-    <row r="68" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="12" t="s">
+    <row r="68" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B68" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D68" s="12" t="s">
+      <c r="D68" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E68" s="12" t="s">
+      <c r="E68" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F68" s="20">
+      <c r="F68" s="19">
         <v>16.649999999999999</v>
       </c>
     </row>
-    <row r="69" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="12"/>
-      <c r="C69" s="12" t="s">
+    <row r="69" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B69" s="11"/>
+      <c r="C69" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F69" s="20">
+      <c r="F69" s="19">
         <v>10.95</v>
       </c>
     </row>
-    <row r="70" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="12" t="s">
+    <row r="70" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B70" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="D70" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E70" s="12" t="s">
+      <c r="E70" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F70" s="20">
+      <c r="F70" s="19">
         <v>9.7200000000000006</v>
       </c>
     </row>
-    <row r="71" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B71" s="12"/>
-      <c r="C71" s="12" t="s">
+    <row r="71" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B71" s="11"/>
+      <c r="C71" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="E71" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F71" s="20">
+      <c r="F71" s="19">
         <v>3.99</v>
       </c>
     </row>
-    <row r="72" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B72" s="12" t="s">
+    <row r="72" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B72" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E72" s="12" t="s">
+      <c r="E72" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F72" s="20">
+      <c r="F72" s="19">
         <v>6.24</v>
       </c>
     </row>
-    <row r="73" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B73" s="12" t="s">
+    <row r="73" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B73" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="13" t="s">
+      <c r="D73" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="E73" s="12" t="s">
+      <c r="E73" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F73" s="20">
+      <c r="F73" s="19">
         <f>570/150</f>
         <v>3.8</v>
       </c>
     </row>
-    <row r="74" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B74" s="12" t="s">
+    <row r="74" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B74" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D74" s="12" t="s">
+      <c r="D74" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E74" s="12" t="s">
+      <c r="E74" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F74" s="20">
+      <c r="F74" s="19">
         <v>3.29</v>
       </c>
     </row>
-    <row r="75" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B75" s="12" t="s">
+    <row r="75" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B75" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="D75" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E75" s="12" t="s">
+      <c r="E75" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F75" s="20"/>
-    </row>
-    <row r="76" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B76" s="12" t="s">
+      <c r="F75" s="19"/>
+    </row>
+    <row r="76" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B76" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="E76" s="12" t="s">
+      <c r="E76" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F76" s="20">
+      <c r="F76" s="19">
         <v>10.8</v>
       </c>
     </row>
-    <row r="77" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B77" s="12" t="s">
+    <row r="77" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B77" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E77" s="12" t="s">
+      <c r="E77" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F77" s="20">
+      <c r="F77" s="19">
         <f>158.36/28</f>
         <v>5.6557142857142866</v>
       </c>
     </row>
-    <row r="78" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B78" s="12" t="s">
+    <row r="78" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B78" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="D78" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E78" s="12" t="s">
+      <c r="E78" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F78" s="20">
+      <c r="F78" s="19">
         <f>98/50</f>
         <v>1.96</v>
       </c>
     </row>
-    <row r="79" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B79" s="12" t="s">
+    <row r="79" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B79" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D79" s="12" t="s">
+      <c r="D79" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E79" s="12" t="s">
+      <c r="E79" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F79" s="20">
+      <c r="F79" s="19">
         <v>12.14</v>
       </c>
     </row>
-    <row r="80" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B80" s="12"/>
-      <c r="C80" s="12" t="s">
+    <row r="80" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B80" s="11"/>
+      <c r="C80" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E80" s="12" t="s">
+      <c r="E80" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F80" s="20">
+      <c r="F80" s="19">
         <v>9.99</v>
       </c>
     </row>
-    <row r="81" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="12" t="s">
+    <row r="81" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B81" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D81" s="12" t="s">
+      <c r="D81" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E81" s="12"/>
-      <c r="F81" s="20"/>
-    </row>
-    <row r="82" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B82" s="12" t="s">
+      <c r="E81" s="11"/>
+      <c r="F81" s="19"/>
+    </row>
+    <row r="82" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B82" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="D82" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E82" s="12"/>
-      <c r="F82" s="20"/>
-    </row>
-    <row r="83" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B83" s="12" t="s">
+      <c r="E82" s="11"/>
+      <c r="F82" s="19"/>
+    </row>
+    <row r="83" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B83" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D83" s="12" t="s">
+      <c r="D83" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E83" s="12" t="s">
+      <c r="E83" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F83" s="20">
+      <c r="F83" s="19">
         <f>62/55.1</f>
         <v>1.1252268602540834</v>
       </c>
     </row>
-    <row r="84" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" s="14" t="s">
+    <row r="84" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B84" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E84" s="12" t="s">
+      <c r="E84" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F84" s="20">
+      <c r="F84" s="19">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="85" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B85" s="14" t="s">
+    <row r="85" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B85" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C85" s="12" t="s">
+      <c r="C85" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E85" s="12" t="s">
+      <c r="E85" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F85" s="20">
+      <c r="F85" s="19">
         <f>340/100</f>
         <v>3.4</v>
       </c>
     </row>
-    <row r="86" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B86" s="14" t="s">
+    <row r="86" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B86" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="C86" s="12" t="s">
+      <c r="C86" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F86" s="20">
+      <c r="F86" s="19">
         <f>460/120</f>
         <v>3.8333333333333335</v>
       </c>
     </row>
-    <row r="87" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="12" t="s">
+    <row r="87" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B87" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="E87" s="12" t="s">
+      <c r="E87" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F87" s="20">
+      <c r="F87" s="19">
         <v>0.26</v>
       </c>
     </row>
-    <row r="88" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B88" s="12" t="s">
+    <row r="88" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B88" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C88" s="12" t="s">
+      <c r="C88" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D88" s="12" t="s">
+      <c r="D88" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="E88" s="12" t="s">
+      <c r="E88" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F88" s="20">
+      <c r="F88" s="19">
         <v>0.25</v>
       </c>
     </row>
-    <row r="89" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="12" t="s">
+    <row r="89" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B89" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="C89" s="12" t="s">
+      <c r="C89" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D89" s="12" t="s">
+      <c r="D89" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="E89" s="12" t="s">
+      <c r="E89" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F89" s="20">
+      <c r="F89" s="19">
         <v>0.84</v>
       </c>
     </row>
-    <row r="90" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="12" t="s">
+    <row r="90" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="E90" s="12"/>
-      <c r="F90" s="20"/>
-    </row>
-    <row r="91" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B91" s="12" t="s">
+      <c r="E90" s="11"/>
+      <c r="F90" s="19"/>
+    </row>
+    <row r="91" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B91" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="C91" s="12" t="s">
+      <c r="C91" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D91" s="12" t="s">
+      <c r="D91" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="E91" s="12"/>
-      <c r="F91" s="20"/>
-    </row>
-    <row r="92" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="12" t="s">
+      <c r="E91" s="11"/>
+      <c r="F91" s="19"/>
+    </row>
+    <row r="92" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B92" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C92" s="12" t="s">
+      <c r="C92" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="D92" s="12" t="s">
+      <c r="D92" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E92" s="12" t="s">
+      <c r="E92" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F92" s="20">
+      <c r="F92" s="19">
         <v>1.52</v>
       </c>
     </row>
-    <row r="93" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B93" s="14" t="s">
+    <row r="93" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B93" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="D93" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="E93" s="12" t="s">
+      <c r="E93" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F93" s="20">
+      <c r="F93" s="19">
         <v>0.9</v>
       </c>
     </row>
-    <row r="94" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B94" s="14" t="s">
+    <row r="94" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B94" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="D94" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="E94" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F94" s="20">
+      <c r="F94" s="19">
         <v>0.72</v>
       </c>
     </row>
-    <row r="95" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B95" s="14" t="s">
+    <row r="95" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B95" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="C95" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="D95" s="12" t="s">
+      <c r="D95" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="E95" s="12" t="s">
+      <c r="E95" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F95" s="20">
+      <c r="F95" s="19">
         <f>358.5/500</f>
         <v>0.71699999999999997</v>
       </c>
     </row>
-    <row r="96" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="12" t="s">
+    <row r="96" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B96" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C96" s="12" t="s">
+      <c r="C96" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E96" s="12" t="s">
+      <c r="E96" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F96" s="20">
+      <c r="F96" s="19">
         <v>0.73</v>
       </c>
     </row>
-    <row r="97" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B97" s="12" t="s">
+    <row r="97" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B97" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C97" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="D97" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="E97" s="12" t="s">
+      <c r="E97" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F97" s="20">
+      <c r="F97" s="19">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="98" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B98" s="12" t="s">
+    <row r="98" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B98" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="C98" s="12" t="s">
+      <c r="C98" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="D98" s="12" t="s">
+      <c r="D98" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E98" s="12" t="s">
+      <c r="E98" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="F98" s="20">
+      <c r="F98" s="19">
         <v>0.98</v>
       </c>
     </row>
-    <row r="99" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B99" s="12" t="s">
+    <row r="99" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B99" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C99" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D99" s="12" t="s">
+      <c r="D99" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="E99" s="12" t="s">
+      <c r="E99" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F99" s="20">
+      <c r="F99" s="19">
         <v>0.43</v>
       </c>
     </row>
-    <row r="100" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B100" s="12" t="s">
+    <row r="100" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B100" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C100" s="12" t="s">
+      <c r="C100" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D100" s="12" t="s">
+      <c r="D100" s="11" t="s">
         <v>215</v>
       </c>
-      <c r="E100" s="12" t="s">
+      <c r="E100" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F100" s="20">
+      <c r="F100" s="19">
         <v>0.42</v>
       </c>
     </row>
-    <row r="101" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B101" s="12" t="s">
+    <row r="101" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B101" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E101" s="12" t="s">
+      <c r="E101" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F101" s="20">
+      <c r="F101" s="19">
         <f>150.83/20</f>
         <v>7.541500000000001</v>
       </c>
     </row>
-    <row r="102" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B102" s="12" t="s">
+    <row r="102" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B102" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="C102" s="12" t="s">
+      <c r="C102" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="E102" s="12" t="s">
+      <c r="E102" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="F102" s="20">
+      <c r="F102" s="19">
         <v>8.99</v>
       </c>
     </row>
-    <row r="103" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B103" s="12" t="s">
+    <row r="103" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B103" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C103" s="12" t="s">
+      <c r="C103" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D103" s="12" t="s">
+      <c r="D103" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E103" s="12" t="s">
+      <c r="E103" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="F103" s="22">
+      <c r="F103" s="20">
         <v>8.49</v>
       </c>
     </row>
-    <row r="104" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B104" s="12" t="s">
+    <row r="104" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B104" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C104" s="12" t="s">
+      <c r="C104" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="D104" s="12" t="s">
+      <c r="D104" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E104" s="12" t="s">
+      <c r="E104" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F104" s="22">
+      <c r="F104" s="20">
         <v>2.2400000000000002</v>
       </c>
     </row>
-    <row r="105" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B105" s="14" t="s">
+    <row r="105" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B105" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C105" s="14" t="s">
+      <c r="C105" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D105" s="14" t="s">
+      <c r="D105" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="E105" s="12" t="s">
+      <c r="E105" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F105" s="22">
+      <c r="F105" s="20">
         <v>0.99</v>
       </c>
     </row>
-    <row r="106" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B106" s="14" t="s">
+    <row r="106" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B106" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C106" s="14" t="s">
+      <c r="C106" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="D106" s="14" t="s">
+      <c r="D106" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="E106" s="12" t="s">
+      <c r="E106" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F106" s="22">
+      <c r="F106" s="20">
         <v>0.82</v>
       </c>
     </row>
-    <row r="107" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B107" s="16" t="s">
+    <row r="107" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B107" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C107" s="12" t="s">
+      <c r="C107" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D107" s="12" t="s">
+      <c r="D107" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="E107" s="12" t="s">
+      <c r="E107" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="F107" s="20"/>
-    </row>
-    <row r="108" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B108" s="12" t="s">
+      <c r="F107" s="19"/>
+    </row>
+    <row r="108" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B108" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="D108" s="12" t="s">
+      <c r="D108" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="E108" s="12" t="s">
+      <c r="E108" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F108" s="20">
+      <c r="F108" s="19">
         <f>210/29.04</f>
         <v>7.2314049586776861</v>
       </c>
     </row>
-    <row r="109" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B109" s="14" t="s">
+    <row r="109" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B109" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C109" s="14" t="s">
+      <c r="C109" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="D109" s="14" t="s">
+      <c r="D109" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="E109" s="12" t="s">
+      <c r="E109" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="F109" s="20">
+      <c r="F109" s="19">
         <v>3.39</v>
       </c>
     </row>
-    <row r="110" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B110" s="14" t="s">
+    <row r="110" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B110" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C110" s="14" t="s">
+      <c r="C110" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="D110" s="14"/>
-      <c r="E110" s="12" t="s">
+      <c r="D110" s="13"/>
+      <c r="E110" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F110" s="20">
+      <c r="F110" s="19">
         <v>3.83</v>
       </c>
     </row>
-    <row r="111" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B111" s="16" t="s">
+    <row r="111" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B111" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C111" s="14" t="s">
+      <c r="C111" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="D111" s="12" t="s">
+      <c r="D111" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E111" s="12" t="s">
+      <c r="E111" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F111" s="20">
+      <c r="F111" s="19">
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="112" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B112" s="16" t="s">
+    <row r="112" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B112" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="C112" s="14" t="s">
+      <c r="C112" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="D112" s="12" t="s">
+      <c r="D112" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="E112" s="12" t="s">
+      <c r="E112" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F112" s="20">
+      <c r="F112" s="19">
         <v>1.25</v>
       </c>
     </row>
-    <row r="113" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B113" s="16" t="s">
+    <row r="113" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B113" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C113" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D113" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E113" s="12" t="s">
+      <c r="E113" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F113" s="20">
+      <c r="F113" s="19">
         <f>340/(44.0925*10)</f>
         <v>0.77110619719907014</v>
       </c>
     </row>
-    <row r="114" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B114" s="24" t="s">
+    <row r="114" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B114" s="22" t="s">
         <v>242</v>
       </c>
-      <c r="C114" s="14" t="s">
+      <c r="C114" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D114" s="14" t="s">
+      <c r="D114" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="E114" s="12" t="s">
+      <c r="E114" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F114" s="20">
+      <c r="F114" s="19">
         <v>1.32</v>
       </c>
     </row>
-    <row r="115" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B115" s="24" t="s">
+    <row r="115" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B115" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="C115" s="14" t="s">
+      <c r="C115" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D115" s="14" t="s">
+      <c r="D115" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="E115" s="12" t="s">
+      <c r="E115" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F115" s="20">
+      <c r="F115" s="19">
         <f>39.74/25.8</f>
         <v>1.5403100775193799</v>
       </c>
     </row>
-    <row r="116" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B116" s="24" t="s">
+    <row r="116" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B116" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="C116" s="14" t="s">
+      <c r="C116" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="D116" s="14" t="s">
+      <c r="D116" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="E116" s="12" t="s">
+      <c r="E116" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F116" s="20">
+      <c r="F116" s="19">
         <f>34.41/12.72</f>
         <v>2.7051886792452828</v>
       </c>
     </row>
-    <row r="117" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B117" s="24" t="s">
+    <row r="117" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B117" s="22" t="s">
         <v>245</v>
       </c>
-      <c r="C117" s="14" t="s">
+      <c r="C117" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="D117" s="14" t="s">
+      <c r="D117" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="E117" s="12" t="s">
+      <c r="E117" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F117" s="20">
+      <c r="F117" s="19">
         <v>3.75</v>
       </c>
     </row>
-    <row r="118" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B118" s="16" t="s">
+    <row r="118" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B118" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C118" s="12" t="s">
+      <c r="C118" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D118" s="12" t="s">
+      <c r="D118" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="E118" s="12" t="s">
+      <c r="E118" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F118" s="20">
+      <c r="F118" s="19">
         <f>59.99/43.7</f>
         <v>1.3727688787185355</v>
       </c>
     </row>
-    <row r="119" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B119" s="16"/>
-      <c r="C119" s="12" t="s">
+    <row r="119" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B119" s="15"/>
+      <c r="C119" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="D119" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="E119" s="12" t="s">
+      <c r="E119" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F119" s="20">
+      <c r="F119" s="19">
         <v>1.4</v>
       </c>
     </row>
-    <row r="120" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B120" s="16" t="s">
+    <row r="120" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B120" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D120" s="12" t="s">
+      <c r="D120" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="E120" s="12" t="s">
+      <c r="E120" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F120" s="20">
+      <c r="F120" s="19">
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="121" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B121" s="16" t="s">
+    <row r="121" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B121" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C121" s="12" t="s">
+      <c r="C121" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D121" s="12" t="s">
+      <c r="D121" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E121" s="12" t="s">
+      <c r="E121" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F121" s="20">
+      <c r="F121" s="19">
         <f>39.88/46.8</f>
         <v>0.85213675213675222</v>
       </c>
     </row>
-    <row r="122" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B122" s="12" t="s">
+    <row r="122" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B122" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D122" s="12" t="s">
+      <c r="D122" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="E122" s="12" t="s">
+      <c r="E122" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F122" s="20">
+      <c r="F122" s="19">
         <v>1.05</v>
       </c>
     </row>
-    <row r="123" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B123" s="12" t="s">
+    <row r="123" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B123" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="C123" s="12" t="s">
+      <c r="C123" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="E123" s="12" t="s">
+      <c r="E123" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="F123" s="20">
+      <c r="F123" s="19">
         <v>5.6</v>
       </c>
     </row>
-    <row r="124" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B124" s="14" t="s">
+    <row r="124" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B124" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C124" s="14" t="s">
+      <c r="C124" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="D124" s="14" t="s">
+      <c r="D124" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="E124" s="12"/>
-      <c r="F124" s="20">
+      <c r="E124" s="11"/>
+      <c r="F124" s="19">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="125" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B125" s="14" t="s">
+    <row r="125" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B125" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="D125" s="14" t="s">
+      <c r="D125" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="E125" s="12" t="s">
+      <c r="E125" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F125" s="20">
+      <c r="F125" s="19">
         <v>0.93</v>
       </c>
     </row>
-    <row r="126" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B126" s="14" t="s">
+    <row r="126" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B126" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="C126" s="14" t="s">
+      <c r="C126" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="D126" s="14" t="s">
+      <c r="D126" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="E126" s="12" t="s">
+      <c r="E126" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F126" s="20">
+      <c r="F126" s="19">
         <f>23.5/29.22</f>
         <v>0.80424366872005482</v>
       </c>
     </row>
-    <row r="127" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B127" s="12" t="s">
+    <row r="127" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B127" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="C127" s="12" t="s">
+      <c r="C127" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E127" s="12" t="s">
+      <c r="E127" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F127" s="20">
+      <c r="F127" s="19">
         <f>264/123.6</f>
         <v>2.1359223300970873</v>
       </c>
     </row>
-    <row r="128" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B128" s="16" t="s">
+    <row r="128" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B128" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="C128" s="12" t="s">
+      <c r="C128" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="D128" s="12" t="s">
+      <c r="D128" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="E128" s="12" t="s">
+      <c r="E128" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F128" s="20">
+      <c r="F128" s="19">
         <f>126.98/(33.6*2)</f>
         <v>1.8895833333333334</v>
       </c>
     </row>
-    <row r="129" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B129" s="16" t="s">
+    <row r="129" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B129" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C129" s="12" t="s">
+      <c r="C129" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="E129" s="12" t="s">
+      <c r="E129" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F129" s="20"/>
-    </row>
-    <row r="130" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B130" s="14" t="s">
+      <c r="F129" s="19"/>
+    </row>
+    <row r="130" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B130" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="C130" s="14" t="s">
+      <c r="C130" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="D130" s="12" t="s">
+      <c r="D130" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="E130" s="12" t="s">
+      <c r="E130" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F130" s="20">
+      <c r="F130" s="19">
         <v>5.08</v>
       </c>
     </row>
-    <row r="131" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B131" s="14" t="s">
+    <row r="131" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B131" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="C131" s="14" t="s">
+      <c r="C131" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="D131" s="12" t="s">
+      <c r="D131" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="E131" s="12" t="s">
+      <c r="E131" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F131" s="20">
+      <c r="F131" s="19">
         <v>5.93</v>
       </c>
     </row>
-    <row r="132" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B132" s="12" t="s">
+    <row r="132" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B132" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="C132" s="12" t="s">
+      <c r="C132" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="D132" s="12" t="s">
+      <c r="D132" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="E132" s="12" t="s">
+      <c r="E132" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F132" s="20">
+      <c r="F132" s="19">
         <v>4.75</v>
       </c>
     </row>
-    <row r="133" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B133" s="16" t="s">
+    <row r="133" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B133" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C133" s="12" t="s">
+      <c r="C133" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="D133" s="12" t="s">
+      <c r="D133" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E133" s="12" t="s">
+      <c r="E133" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F133" s="20">
+      <c r="F133" s="19">
         <f>36.67/33.2</f>
         <v>1.1045180722891565</v>
       </c>
     </row>
-    <row r="134" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B134" s="16"/>
-      <c r="C134" s="12" t="s">
+    <row r="134" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B134" s="15"/>
+      <c r="C134" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="D134" s="12" t="s">
+      <c r="D134" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="E134" s="12" t="s">
+      <c r="E134" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F134" s="20">
+      <c r="F134" s="19">
         <v>1.2</v>
       </c>
     </row>
-    <row r="135" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B135" s="12" t="s">
+    <row r="135" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B135" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="C135" s="12" t="s">
+      <c r="C135" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="D135" s="12" t="s">
+      <c r="D135" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="E135" s="12" t="s">
+      <c r="E135" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F135" s="20">
+      <c r="F135" s="19">
         <v>1.29</v>
       </c>
     </row>
-    <row r="136" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B136" s="12" t="s">
+    <row r="136" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B136" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="C136" s="12" t="s">
+      <c r="C136" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="D136" s="12" t="s">
+      <c r="D136" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="E136" s="12" t="s">
+      <c r="E136" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F136" s="20">
+      <c r="F136" s="19">
         <v>0.96</v>
       </c>
     </row>
-    <row r="137" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B137" s="14" t="s">
+    <row r="137" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B137" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="C137" s="24" t="s">
+      <c r="C137" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="D137" s="24" t="s">
+      <c r="D137" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="E137" s="16" t="s">
+      <c r="E137" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F137" s="20">
+      <c r="F137" s="19">
         <v>0.61</v>
       </c>
     </row>
-    <row r="138" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B138" s="14" t="s">
+    <row r="138" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B138" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="C138" s="24" t="s">
+      <c r="C138" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="D138" s="24" t="s">
+      <c r="D138" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="E138" s="16" t="s">
+      <c r="E138" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F138" s="20">
+      <c r="F138" s="19">
         <f>26.5/50</f>
         <v>0.53</v>
       </c>
     </row>
-    <row r="139" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B139" s="14" t="s">
+    <row r="139" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B139" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="C139" s="24" t="s">
+      <c r="C139" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="D139" s="24" t="s">
+      <c r="D139" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="E139" s="16" t="s">
+      <c r="E139" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F139" s="20">
+      <c r="F139" s="19">
         <v>0.87</v>
       </c>
     </row>
-    <row r="140" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B140" s="14" t="s">
+    <row r="140" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B140" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="C140" s="24" t="s">
+      <c r="C140" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="D140" s="24" t="s">
+      <c r="D140" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="E140" s="16" t="s">
+      <c r="E140" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F140" s="20">
+      <c r="F140" s="19">
         <v>0.84</v>
       </c>
     </row>
-    <row r="141" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B141" s="14" t="s">
+    <row r="141" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B141" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="C141" s="24" t="s">
+      <c r="C141" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="D141" s="24" t="s">
+      <c r="D141" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="E141" s="16" t="s">
+      <c r="E141" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F141" s="20">
+      <c r="F141" s="19">
         <v>1.03</v>
       </c>
     </row>
-    <row r="142" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B142" s="12" t="s">
+    <row r="142" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B142" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="C142" s="16" t="s">
+      <c r="C142" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="D142" s="16" t="s">
+      <c r="D142" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="E142" s="16" t="s">
+      <c r="E142" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="F142" s="20">
+      <c r="F142" s="19">
         <f>891/1650</f>
         <v>0.54</v>
       </c>
     </row>
-    <row r="143" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B143" s="13" t="s">
+    <row r="143" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B143" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C143" s="17" t="s">
+      <c r="C143" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="D143" s="16" t="s">
+      <c r="D143" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="E143" s="16" t="s">
+      <c r="E143" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F143" s="20">
+      <c r="F143" s="19">
         <v>1.52</v>
       </c>
     </row>
-    <row r="144" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B144" s="13" t="s">
+    <row r="144" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B144" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="C144" s="17" t="s">
+      <c r="C144" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="D144" s="16" t="s">
+      <c r="D144" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="E144" s="16" t="s">
+      <c r="E144" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="F144" s="20">
+      <c r="F144" s="19">
         <v>3.01</v>
       </c>
     </row>
-    <row r="145" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B145" s="13" t="s">
+    <row r="145" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B145" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="C145" s="17" t="s">
+      <c r="C145" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="D145" s="16" t="s">
+      <c r="D145" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="E145" s="16" t="s">
+      <c r="E145" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="F145" s="20"/>
-    </row>
-    <row r="146" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B146" s="16" t="s">
+      <c r="F145" s="19"/>
+    </row>
+    <row r="146" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B146" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="C146" s="12" t="s">
+      <c r="C146" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="D146" s="12" t="s">
+      <c r="D146" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="E146" s="12" t="s">
+      <c r="E146" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="F146" s="20">
+      <c r="F146" s="19">
         <f>450/255</f>
         <v>1.7647058823529411</v>
       </c>
     </row>
-    <row r="147" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B147" s="14" t="s">
+    <row r="147" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B147" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="C147" s="24" t="s">
+      <c r="C147" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="D147" s="24" t="s">
+      <c r="D147" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="E147" s="16" t="s">
+      <c r="E147" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="F147" s="20">
+      <c r="F147" s="19">
         <v>2.08</v>
       </c>
     </row>
-    <row r="148" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B148" s="14" t="s">
+    <row r="148" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B148" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="C148" s="24" t="s">
+      <c r="C148" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="D148" s="24" t="s">
+      <c r="D148" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="E148" s="16" t="s">
+      <c r="E148" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F148" s="20">
+      <c r="F148" s="19">
         <f>860/(20*29.10102)</f>
         <v>1.4776114376746932</v>
       </c>
     </row>
-    <row r="149" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B149" s="12" t="s">
+    <row r="149" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B149" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="C149" s="12" t="s">
+      <c r="C149" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="D149" s="12" t="s">
+      <c r="D149" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="E149" s="12" t="s">
+      <c r="E149" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F149" s="20">
+      <c r="F149" s="19">
         <v>0.88</v>
       </c>
     </row>
-    <row r="150" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B150" s="14" t="s">
+    <row r="150" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B150" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="C150" s="14" t="s">
+      <c r="C150" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="D150" s="14" t="s">
+      <c r="D150" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="E150" s="14" t="s">
+      <c r="E150" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F150" s="20">
+      <c r="F150" s="19">
         <f>37.11/42</f>
         <v>0.88357142857142856</v>
       </c>
     </row>
-    <row r="151" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B151" s="14" t="s">
+    <row r="151" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B151" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="C151" s="14" t="s">
+      <c r="C151" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="D151" s="14" t="s">
+      <c r="D151" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="E151" s="14" t="s">
+      <c r="E151" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F151" s="20"/>
-    </row>
-    <row r="152" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B152" s="12" t="s">
+      <c r="F151" s="19"/>
+    </row>
+    <row r="152" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B152" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="C152" s="16" t="s">
+      <c r="C152" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="D152" s="16" t="s">
+      <c r="D152" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="E152" s="16" t="s">
+      <c r="E152" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="F152" s="20">
+      <c r="F152" s="19">
         <v>1.39</v>
       </c>
     </row>
-    <row r="153" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B153" s="16" t="s">
+    <row r="153" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B153" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C153" s="14" t="s">
+      <c r="C153" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="D153" s="12" t="s">
+      <c r="D153" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="E153" s="12" t="s">
+      <c r="E153" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F153" s="20">
+      <c r="F153" s="19">
         <v>2.15</v>
       </c>
     </row>
-    <row r="154" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B154" s="16" t="s">
+    <row r="154" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B154" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C154" s="14" t="s">
+      <c r="C154" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="D154" s="12" t="s">
+      <c r="D154" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E154" s="12" t="s">
+      <c r="E154" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F154" s="20">
+      <c r="F154" s="19">
         <f>12.42/33.88</f>
         <v>0.36658795749704837</v>
       </c>
     </row>
-    <row r="155" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B155" s="16" t="s">
+    <row r="155" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B155" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="C155" s="12" t="s">
+      <c r="C155" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="D155" s="12" t="s">
+      <c r="D155" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="E155" s="12" t="s">
+      <c r="E155" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="F155" s="20">
+      <c r="F155" s="19">
         <f>25/76</f>
         <v>0.32894736842105265</v>
       </c>
     </row>
-    <row r="156" spans="2:6" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B156" s="16" t="s">
+    <row r="156" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B156" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D156" s="12" t="s">
+      <c r="D156" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="E156" s="12" t="s">
+      <c r="E156" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="F156" s="20">
+      <c r="F156" s="19">
         <f>27.09/36.8</f>
         <v>0.7361413043478261</v>
       </c>

--- a/Ingredients Price table Web.xlsx
+++ b/Ingredients Price table Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C0AC37-D168-41FB-A475-BD1C2386C7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F5E27F-34B8-4358-9FA1-D75B746F06DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69CAB99C-E3EE-4D15-B6BE-5479B7A51CB5}"/>
   </bookViews>
@@ -1021,26 +1021,11 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1054,8 +1039,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1072,6 +1074,18 @@
       <patternFill patternType="solid">
         <fgColor theme="2"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1099,44 +1113,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1144,29 +1138,57 @@
     <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="7" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{39CE6146-415C-49C7-A183-C44FB8124368}"/>
   </cellStyles>
@@ -1503,27 +1525,27 @@
   <dimension ref="A1:E1022"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" style="20" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" style="20" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="9" style="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="9" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1531,16 +1553,16 @@
       <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>2.35</v>
       </c>
     </row>
@@ -1548,472 +1570,482 @@
       <c r="A3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="10">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="15"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="10">
         <v>1.62</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="10">
         <v>1.92</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="9">
         <v>5.19</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="10">
         <v>6.73</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="10">
+        <f>68.49/50</f>
         <v>1.3697999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="9">
         <v>4.3899999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="10">
         <v>3.29</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="9">
         <v>1.99</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="10">
         <v>5.99</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="10">
+        <f>1674/600</f>
         <v>2.79</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="10">
         <v>0.59</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="9">
+        <f>86.36/40</f>
         <v>2.1589999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="10">
+        <f>586.89/300</f>
         <v>1.9562999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="10">
         <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="9">
         <v>2.25</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="9">
+        <f>2511.34/(26*40)</f>
         <v>2.4147500000000002</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="10">
         <v>1.39</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="10">
+        <f>27/(4.4*4)</f>
         <v>1.5340909090909089</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="9">
         <v>2.31</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6" t="s">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="10">
+        <f>80.31/30</f>
         <v>2.677</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="14"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="9"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="14"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="9"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="10">
+        <f>829.9/(22*10)</f>
         <v>3.772272727272727</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="10">
+        <f>49/25</f>
         <v>1.96</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="14"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6" t="s">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="10">
+        <f>1256/(6.61387*4*20)</f>
         <v>2.3737993035847396</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="14"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E32" s="14">
@@ -2021,507 +2053,521 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E33" s="9">
         <v>2.19</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E34" s="10">
+        <f>1896.49/953.06</f>
         <v>1.9898957043627894</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="10">
         <v>2.57</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E36" s="10">
+        <f>192/144</f>
         <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E37" s="14">
+      <c r="E37" s="10">
+        <f>33.78/22.05</f>
         <v>1.5319727891156463</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="10">
+        <f>32.24/22.05</f>
         <v>1.4621315192743765</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E39" s="14">
+      <c r="E39" s="10">
         <v>0.9</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E40" s="14">
+      <c r="E40" s="10">
         <v>0.98</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E41" s="14">
+      <c r="E41" s="10">
+        <f>368/120</f>
         <v>3.0666666666666669</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6" t="s">
+      <c r="C42" s="8"/>
+      <c r="D42" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E42" s="14">
+      <c r="E42" s="10">
         <v>2.1320000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E43" s="14">
+      <c r="E43" s="9">
         <v>0.89</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="10"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6" t="s">
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="9">
         <v>0.99</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6" t="s">
+      <c r="B45" s="12"/>
+      <c r="C45" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="10">
+        <f>60.43/38</f>
         <v>1.5902631578947368</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6" t="s">
+      <c r="B46" s="12"/>
+      <c r="C46" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="9">
+        <f>86/76</f>
         <v>1.131578947368421</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="14">
+      <c r="E47" s="9">
         <v>4.99</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E48" s="14">
+      <c r="E48" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E49" s="14">
+      <c r="E49" s="15">
         <v>0.99</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="E50" s="14">
+      <c r="E50" s="9">
         <v>54.54</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6" t="s">
+      <c r="A51" s="12"/>
+      <c r="B51" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E51" s="14">
+      <c r="E51" s="10">
         <v>5.67</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="E52" s="14">
+      <c r="E52" s="10">
+        <f>45.25/25</f>
         <v>1.81</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E53" s="14">
+      <c r="E53" s="10">
+        <f>690/132</f>
         <v>5.2272727272727275</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E54" s="14">
+      <c r="E54" s="10">
         <v>5.59</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="14">
+      <c r="E55" s="10">
+        <f>136.47/20</f>
         <v>6.8235000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="14">
+      <c r="E56" s="9">
         <v>7.19</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E57" s="14">
+      <c r="E57" s="9">
         <v>6.6</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="14"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="9"/>
     </row>
     <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="14">
+      <c r="E59" s="10">
+        <f>60.99/50</f>
         <v>1.2198</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E60" s="14">
+      <c r="E60" s="10">
         <v>1.56</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6" t="s">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E61" s="14">
+      <c r="E61" s="9">
+        <f>45.95/25</f>
         <v>1.8380000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6" t="s">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E62" s="14">
+      <c r="E62" s="10">
+        <f>45.95/50</f>
         <v>0.91900000000000004</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E63" s="14">
+      <c r="E63" s="10">
+        <f>48.16/20</f>
         <v>2.4079999999999999</v>
       </c>
     </row>
@@ -2529,16 +2575,16 @@
       <c r="A64" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E64" s="14">
+      <c r="E64" s="9">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2546,629 +2592,637 @@
       <c r="A65" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E65" s="14">
+      <c r="E65" s="9">
         <v>6.34</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="E66" s="14">
+      <c r="E66" s="9">
         <v>4.8</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E67" s="14">
+      <c r="E67" s="9">
         <v>2.68</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E68" s="14">
+      <c r="E68" s="9">
         <v>16.649999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6" t="s">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E69" s="14">
+      <c r="E69" s="9">
         <v>10.95</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E70" s="14">
+      <c r="E70" s="9">
         <v>9.7200000000000006</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="10"/>
-      <c r="B71" s="6" t="s">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E71" s="14">
+      <c r="E71" s="9">
         <v>3.99</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E72" s="14">
+      <c r="E72" s="9">
         <v>6.24</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E73" s="14">
+      <c r="E73" s="10">
+        <f>570/150</f>
         <v>3.8</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E74" s="14">
+      <c r="E74" s="9">
         <v>3.29</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E75" s="14">
+      <c r="E75" s="10">
         <v>9.07</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E76" s="14">
+      <c r="E76" s="9">
         <v>10.8</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E77" s="14">
+      <c r="E77" s="10">
+        <f>158.36/28</f>
         <v>5.6557142857142866</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E78" s="14">
+      <c r="E78" s="10">
+        <f>98/50</f>
         <v>1.96</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="D79" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E79" s="14">
+      <c r="E79" s="10">
         <v>18.89</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="10"/>
-      <c r="B80" s="6" t="s">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E80" s="14">
+      <c r="E80" s="9">
         <v>9.99</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D81" s="6"/>
-      <c r="E81" s="14"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="17"/>
     </row>
     <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D82" s="6"/>
-      <c r="E82" s="15"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="9"/>
     </row>
     <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D83" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E83" s="14">
+      <c r="E83" s="10">
+        <f>62/55.1</f>
         <v>1.1252268602540834</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="D84" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E84" s="14">
+      <c r="E84" s="9">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="D85" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E85" s="14">
+      <c r="E85" s="10">
+        <f>340/100</f>
         <v>3.4</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E86" s="14">
+      <c r="E86" s="10">
+        <f>460/120</f>
         <v>3.8333333333333335</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E87" s="14">
+      <c r="E87" s="10">
         <v>0.26</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D88" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E88" s="14">
+      <c r="E88" s="9">
         <v>0.25</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="D89" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E89" s="14">
+      <c r="E89" s="9">
         <v>0.84</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D90" s="6"/>
-      <c r="E90" s="14"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="9"/>
     </row>
     <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D91" s="6"/>
-      <c r="E91" s="14"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="9"/>
     </row>
     <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="D92" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E92" s="14">
+      <c r="E92" s="9">
         <v>1.52</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C93" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="D93" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E93" s="14">
+      <c r="E93" s="10">
         <v>0.84</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6" t="s">
+      <c r="A94" s="12"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E94" s="14">
+      <c r="E94" s="9">
         <v>0.72</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6" t="s">
+      <c r="A95" s="12"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D95" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E95" s="14">
+      <c r="E95" s="10">
+        <f>358.5/500</f>
         <v>0.71699999999999997</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="D96" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E96" s="14">
+      <c r="E96" s="10">
         <v>0.73</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E97" s="14">
+      <c r="E97" s="10">
         <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="E98" s="14">
+      <c r="E98" s="9">
         <v>0.98</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="C99" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E99" s="14">
+      <c r="E99" s="10">
         <v>0.48</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B100" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="D100" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E100" s="14">
+      <c r="E100" s="9">
         <v>0.42</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C101" s="6" t="s">
+      <c r="C101" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="D101" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E101" s="14">
+      <c r="E101" s="10">
+        <f>150.83/20</f>
         <v>7.541500000000001</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E102" s="14">
+      <c r="E102" s="9">
         <v>8.99</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A103" s="10" t="s">
+      <c r="A103" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C103" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="D103" s="8" t="s">
         <v>218</v>
       </c>
       <c r="E103" s="14">
@@ -3176,16 +3230,16 @@
       </c>
     </row>
     <row r="104" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A104" s="10" t="s">
+      <c r="A104" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="D104" s="8" t="s">
         <v>49</v>
       </c>
       <c r="E104" s="14">
@@ -3193,16 +3247,16 @@
       </c>
     </row>
     <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="D105" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E105" s="14">
@@ -3210,10 +3264,10 @@
       </c>
     </row>
     <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6" t="s">
+      <c r="A106" s="12"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E106" s="14">
@@ -3221,588 +3275,600 @@
       </c>
     </row>
     <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C107" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D107" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="E107" s="14">
+      <c r="E107" s="10">
         <v>5.67</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="B108" s="6" t="s">
+      <c r="B108" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="D108" s="6" t="s">
+      <c r="D108" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E108" s="14">
+      <c r="E108" s="10">
+        <f>210/29.04</f>
         <v>7.2314049586776861</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D109" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E109" s="14">
+      <c r="E109" s="9">
         <v>3.39</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6" t="s">
+      <c r="A110" s="12"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E110" s="14">
+      <c r="E110" s="9">
         <v>3.83</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B111" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D111" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E111" s="14">
+      <c r="E111" s="9">
         <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6" t="s">
+      <c r="B112" s="12"/>
+      <c r="C112" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="D112" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E112" s="14">
+      <c r="E112" s="9">
         <v>1.25</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6" t="s">
+      <c r="B113" s="12"/>
+      <c r="C113" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D113" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E113" s="14">
+      <c r="E113" s="10">
+        <f>340/(44.0925*10)</f>
         <v>0.77110619719907014</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="B114" s="6" t="s">
+      <c r="B114" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D114" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E114" s="14">
+      <c r="E114" s="9">
         <v>1.32</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="10"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6" t="s">
+      <c r="A115" s="19"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E115" s="14">
+      <c r="E115" s="10">
+        <f>39.74/25.8</f>
         <v>1.5403100775193799</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="C116" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="D116" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E116" s="14">
+      <c r="E116" s="9">
+        <f>34.41/12.72</f>
         <v>2.7051886792452828</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6" t="s">
+      <c r="A117" s="19"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E117" s="14">
+      <c r="E117" s="9">
         <v>3.75</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E118" s="14">
+      <c r="E118" s="10">
+        <f>59.99/43.7</f>
         <v>1.3727688787185355</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="6"/>
-      <c r="B119" s="10" t="s">
+      <c r="A119" s="18"/>
+      <c r="B119" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C119" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D119" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E119" s="14">
+      <c r="E119" s="9">
         <v>1.4</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B120" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C120" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E120" s="14">
+      <c r="E120" s="9">
         <v>1.1100000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B121" s="10" t="s">
+      <c r="B121" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C121" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D121" s="10" t="s">
+      <c r="D121" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E121" s="14">
+      <c r="E121" s="10">
+        <f>39.88/46.8</f>
         <v>0.85213675213675222</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B122" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C122" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E122" s="14">
+      <c r="E122" s="9">
         <v>1.05</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B123" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C123" s="10" t="s">
+      <c r="C123" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="E123" s="14">
+      <c r="E123" s="9">
         <v>5.6</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B124" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C124" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D124" s="10"/>
-      <c r="E124" s="14">
+      <c r="D124" s="8"/>
+      <c r="E124" s="9">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="7"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="10"/>
-      <c r="D125" s="10" t="s">
+      <c r="A125" s="12"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="12"/>
+      <c r="D125" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="E125" s="14">
+      <c r="E125" s="10">
         <v>0.8</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="7"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="10"/>
-      <c r="D126" s="10" t="s">
+      <c r="A126" s="12"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="12"/>
+      <c r="D126" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E126" s="14">
+      <c r="E126" s="9">
+        <f>23.5/29.22</f>
         <v>0.80424366872005482</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
+      <c r="A127" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="B127" s="11" t="s">
+      <c r="B127" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C127" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="D127" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E127" s="14">
+      <c r="E127" s="10">
+        <f>264/123.6</f>
         <v>2.1359223300970873</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="B128" s="6" t="s">
+      <c r="B128" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C128" s="6" t="s">
+      <c r="C128" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D128" s="6" t="s">
+      <c r="D128" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E128" s="14">
+      <c r="E128" s="10">
+        <f>126.98/(33.6*2)</f>
         <v>1.8895833333333334</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="B129" s="6" t="s">
+      <c r="B129" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D129" s="6" t="s">
+      <c r="D129" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E129" s="14"/>
+      <c r="E129" s="9"/>
     </row>
     <row r="130" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="10" t="s">
+      <c r="A130" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="B130" s="6" t="s">
+      <c r="B130" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="C130" s="6" t="s">
+      <c r="C130" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="D130" s="6" t="s">
+      <c r="D130" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E130" s="14">
+      <c r="E130" s="10">
         <v>5.08</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6" t="s">
+      <c r="A131" s="12"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="D131" s="6" t="s">
+      <c r="D131" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E131" s="14">
+      <c r="E131" s="9">
         <v>5.93</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="6" t="s">
+      <c r="A132" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="B132" s="6" t="s">
+      <c r="B132" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="C132" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D132" s="6" t="s">
+      <c r="D132" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E132" s="14">
+      <c r="E132" s="9">
         <v>4.75</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6" t="s">
+      <c r="A133" s="8"/>
+      <c r="B133" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C133" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="D133" s="6" t="s">
+      <c r="D133" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E133" s="14">
+      <c r="E133" s="21">
         <v>3.6857142857142855</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="6" t="s">
+      <c r="A134" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="B134" s="6" t="s">
+      <c r="B134" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="C134" s="6" t="s">
+      <c r="C134" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D134" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E134" s="14">
+      <c r="E134" s="10">
+        <f>36.67/33.2</f>
         <v>1.1045180722891565</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="6"/>
-      <c r="B135" s="10" t="s">
+      <c r="A135" s="18"/>
+      <c r="B135" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="C135" s="10" t="s">
+      <c r="C135" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="D135" s="10" t="s">
+      <c r="D135" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E135" s="14">
+      <c r="E135" s="9">
         <v>1.2</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="6" t="s">
+      <c r="A136" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="B136" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C136" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D136" s="10" t="s">
+      <c r="D136" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E136" s="14">
+      <c r="E136" s="10">
         <v>1.2946979038224415</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="B137" s="6" t="s">
+      <c r="B137" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C137" s="6" t="s">
+      <c r="C137" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D137" s="6" t="s">
+      <c r="D137" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E137" s="14">
+      <c r="E137" s="9">
         <v>0.96</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="6" t="s">
+      <c r="A138" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="B138" s="6" t="s">
+      <c r="B138" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="C138" s="6" t="s">
+      <c r="C138" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="D138" s="6" t="s">
+      <c r="D138" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E138" s="14">
+      <c r="E138" s="9">
         <v>0.61</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6" t="s">
+      <c r="A139" s="12"/>
+      <c r="B139" s="19"/>
+      <c r="C139" s="19"/>
+      <c r="D139" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E139" s="14">
+      <c r="E139" s="9">
+        <f>26.5/50</f>
         <v>0.53</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="6" t="s">
+      <c r="A140" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6" t="s">
+      <c r="B140" s="19"/>
+      <c r="C140" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="D140" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E140" s="14">
+      <c r="E140" s="9">
         <v>0.87</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6" t="s">
+      <c r="A141" s="12"/>
+      <c r="B141" s="19"/>
+      <c r="C141" s="19"/>
+      <c r="D141" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E141" s="14">
+      <c r="E141" s="10">
         <v>0.84</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6" t="s">
+      <c r="A142" s="12"/>
+      <c r="B142" s="19"/>
+      <c r="C142" s="19"/>
+      <c r="D142" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E142" s="14">
+      <c r="E142" s="9">
         <v>1.03</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="6" t="s">
+      <c r="A143" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B143" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C143" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="D143" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E143" s="14">
+      <c r="E143" s="10">
+        <f>891/1650</f>
         <v>0.54</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="6" t="s">
+      <c r="A144" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B144" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C144" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="D144" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E144" s="14">
+      <c r="E144" s="9">
         <v>1.52</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="17" t="s">
+    <row r="145" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A145" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B145" s="22" t="s">
         <v>282</v>
       </c>
       <c r="C145" s="18" t="s">
@@ -3811,217 +3877,222 @@
       <c r="D145" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E145" s="14">
+      <c r="E145" s="9">
         <v>3.01</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="6" t="s">
+      <c r="A146" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="B146" s="6" t="s">
+      <c r="B146" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="C146" s="6" t="s">
+      <c r="C146" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="D146" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="E146" s="14"/>
+      <c r="E146" s="9"/>
     </row>
     <row r="147" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="6" t="s">
+      <c r="A147" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="B147" s="6" t="s">
+      <c r="B147" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="C147" s="6" t="s">
+      <c r="C147" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="D147" s="6" t="s">
+      <c r="D147" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E147" s="14">
+      <c r="E147" s="10">
+        <f>450/255</f>
         <v>1.7647058823529411</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="6" t="s">
+      <c r="A148" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="B148" s="6" t="s">
+      <c r="B148" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="C148" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="D148" s="6" t="s">
+      <c r="D148" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E148" s="14">
+      <c r="E148" s="9">
         <v>2.08</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6" t="s">
+      <c r="A149" s="12"/>
+      <c r="B149" s="19"/>
+      <c r="C149" s="19"/>
+      <c r="D149" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E149" s="14">
+      <c r="E149" s="10">
+        <f>860/(20*29.10102)</f>
         <v>1.4776114376746932</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A150" s="10" t="s">
+      <c r="A150" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="B150" s="6" t="s">
+      <c r="B150" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C150" s="6" t="s">
+      <c r="C150" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="D150" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E150" s="14">
+      <c r="E150" s="9">
         <v>0.88</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="10" t="s">
+      <c r="A151" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="B151" s="6" t="s">
+      <c r="B151" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="C151" s="6" t="s">
+      <c r="C151" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="D151" s="6" t="s">
+      <c r="D151" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E151" s="14">
+      <c r="E151" s="10">
         <v>0.88</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="10"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="14"/>
+      <c r="A152" s="12"/>
+      <c r="B152" s="12"/>
+      <c r="C152" s="12"/>
+      <c r="D152" s="12"/>
+      <c r="E152" s="9"/>
     </row>
     <row r="153" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="10" t="s">
+      <c r="A153" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="B153" s="6" t="s">
+      <c r="B153" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="C153" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="D153" s="6" t="s">
+      <c r="D153" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="E153" s="14">
+      <c r="E153" s="9">
         <v>1.39</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="6" t="s">
+      <c r="A154" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="B154" s="6" t="s">
+      <c r="B154" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="C154" s="6" t="s">
+      <c r="C154" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="D154" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E154" s="15">
+      <c r="E154" s="9">
         <v>2.15</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="6" t="s">
+      <c r="A155" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="B155" s="6"/>
-      <c r="C155" s="6" t="s">
+      <c r="B155" s="12"/>
+      <c r="C155" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D155" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E155" s="16">
+      <c r="E155" s="9">
+        <f>12.42/33.88</f>
         <v>0.36658795749704837</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="19" t="s">
+    <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A156" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="B156" s="19" t="s">
+      <c r="B156" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="C156" s="19" t="s">
+      <c r="C156" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D156" s="19" t="s">
+      <c r="D156" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E156" s="19">
+      <c r="E156" s="10">
+        <f>25/76</f>
         <v>0.32894736842105265</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="2"/>
-      <c r="B157" s="2" t="s">
+      <c r="A157" s="18"/>
+      <c r="B157" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="C157" s="2" t="s">
+      <c r="C157" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="D157" s="2"/>
-      <c r="E157" s="3">
+      <c r="D157" s="8"/>
+      <c r="E157" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="2"/>
-      <c r="B158" s="2" t="s">
+      <c r="A158" s="18"/>
+      <c r="B158" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="D158" s="2"/>
-      <c r="E158" s="3">
+      <c r="D158" s="8"/>
+      <c r="E158" s="10">
         <v>0.94</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="2" t="s">
+      <c r="A159" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B159" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="C159" s="2" t="s">
+      <c r="C159" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="D159" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E159" s="3">
+      <c r="E159" s="10">
+        <f>27.09/36.8</f>
         <v>0.7361413043478261</v>
       </c>
     </row>
@@ -10072,7 +10143,52 @@
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <mergeCells count="43">
+    <mergeCell ref="D151:D152"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A148:A149"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="C151:C152"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="A138:A139"/>
+    <mergeCell ref="B138:B142"/>
+    <mergeCell ref="C138:C139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="C140:C142"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="C116:C117"/>
+    <mergeCell ref="A124:A126"/>
+    <mergeCell ref="B124:B126"/>
+    <mergeCell ref="C124:C126"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="A109:A110"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="B93:B95"/>
+    <mergeCell ref="A105:A106"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B46"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Ingredients Price table Web.xlsx
+++ b/Ingredients Price table Web.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProductWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F5E27F-34B8-4358-9FA1-D75B746F06DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1121F5D7-4494-44B8-854F-E3A546EC013B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69CAB99C-E3EE-4D15-B6BE-5479B7A51CB5}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="314">
   <si>
     <t>Code</t>
   </si>
@@ -1089,7 +1089,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1110,6 +1110,19 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1154,9 +1167,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1174,9 +1184,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1185,6 +1192,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1522,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA673556-6469-4516-B6CA-C76DCD1ABD75}">
-  <dimension ref="A1:E1022"/>
+  <dimension ref="A1:E1021"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="7" customWidth="1"/>
@@ -1903,10 +1916,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="8" t="s">
@@ -1920,8 +1933,12 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
+      <c r="A24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>51</v>
+      </c>
       <c r="C24" s="8" t="s">
         <v>53</v>
       </c>
@@ -1982,7 +1999,7 @@
       <c r="B28" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="12" t="s">
         <v>49</v>
       </c>
       <c r="D28" s="8" t="s">
@@ -1994,13 +2011,13 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>66</v>
       </c>
       <c r="D29" s="8" t="s">
@@ -2009,9 +2026,15 @@
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
+      <c r="A30" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>66</v>
+      </c>
       <c r="D30" s="8" t="s">
         <v>66</v>
       </c>
@@ -2048,7 +2071,7 @@
       <c r="D32" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="13">
         <v>2.0499999999999998</v>
       </c>
     </row>
@@ -2226,10 +2249,10 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="11" t="s">
         <v>96</v>
       </c>
       <c r="C43" s="8" t="s">
@@ -2243,8 +2266,12 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
+      <c r="A44" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="C44" s="8" t="s">
         <v>38</v>
       </c>
@@ -2259,7 +2286,9 @@
       <c r="A45" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B45" s="12"/>
+      <c r="B45" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="C45" s="8" t="s">
         <v>99</v>
       </c>
@@ -2275,7 +2304,9 @@
       <c r="A46" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B46" s="12"/>
+      <c r="B46" s="11" t="s">
+        <v>96</v>
+      </c>
       <c r="C46" s="8" t="s">
         <v>101</v>
       </c>
@@ -2334,12 +2365,12 @@
       <c r="D49" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="14">
         <v>0.99</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="11" t="s">
         <v>109</v>
       </c>
       <c r="B50" s="8" t="s">
@@ -2356,7 +2387,9 @@
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="12"/>
+      <c r="A51" s="11" t="s">
+        <v>109</v>
+      </c>
       <c r="B51" s="8" t="s">
         <v>110</v>
       </c>
@@ -2377,10 +2410,10 @@
       <c r="B52" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C52" s="16" t="s">
+      <c r="C52" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="15" t="s">
         <v>115</v>
       </c>
       <c r="E52" s="10">
@@ -2507,10 +2540,10 @@
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="11" t="s">
         <v>135</v>
       </c>
       <c r="C60" s="8" t="s">
@@ -2524,8 +2557,12 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
+      <c r="A61" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>135</v>
+      </c>
       <c r="C61" s="8" t="s">
         <v>133</v>
       </c>
@@ -2710,7 +2747,7 @@
       <c r="B72" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" s="12" t="s">
         <v>69</v>
       </c>
       <c r="D72" s="8" t="s">
@@ -2727,7 +2764,7 @@
       <c r="B73" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="12" t="s">
         <v>157</v>
       </c>
       <c r="D73" s="8" t="s">
@@ -2868,7 +2905,7 @@
         <v>69</v>
       </c>
       <c r="D81" s="8"/>
-      <c r="E81" s="17"/>
+      <c r="E81" s="16"/>
     </row>
     <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
@@ -3049,10 +3086,10 @@
       </c>
     </row>
     <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A93" s="12" t="s">
+      <c r="A93" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="11" t="s">
         <v>199</v>
       </c>
       <c r="C93" s="8" t="s">
@@ -3066,8 +3103,12 @@
       </c>
     </row>
     <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A94" s="12"/>
-      <c r="B94" s="12"/>
+      <c r="A94" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>199</v>
+      </c>
       <c r="C94" s="8" t="s">
         <v>133</v>
       </c>
@@ -3079,8 +3120,12 @@
       </c>
     </row>
     <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A95" s="12"/>
-      <c r="B95" s="12"/>
+      <c r="A95" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>199</v>
+      </c>
       <c r="C95" s="8" t="s">
         <v>133</v>
       </c>
@@ -3225,7 +3270,7 @@
       <c r="D103" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="E103" s="14">
+      <c r="E103" s="13">
         <v>8.49</v>
       </c>
     </row>
@@ -3242,40 +3287,46 @@
       <c r="D104" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E104" s="14">
+      <c r="E104" s="13">
         <v>2.2400000000000002</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="C105" s="12" t="s">
+      <c r="C105" s="11" t="s">
         <v>223</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E105" s="14">
+      <c r="E105" s="13">
         <v>0.99</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A106" s="12"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
+      <c r="A106" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>223</v>
+      </c>
       <c r="D106" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E106" s="14">
+      <c r="E106" s="13">
         <v>0.82</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A107" s="18" t="s">
+      <c r="A107" s="17" t="s">
         <v>224</v>
       </c>
       <c r="B107" s="8" t="s">
@@ -3310,13 +3361,13 @@
       </c>
     </row>
     <row r="109" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B109" s="12" t="s">
+      <c r="B109" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C109" s="11" t="s">
         <v>232</v>
       </c>
       <c r="D109" s="8" t="s">
@@ -3327,9 +3378,15 @@
       </c>
     </row>
     <row r="110" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A110" s="12"/>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
+      <c r="A110" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C110" s="11" t="s">
+        <v>232</v>
+      </c>
       <c r="D110" s="8" t="s">
         <v>54</v>
       </c>
@@ -3338,10 +3395,10 @@
       </c>
     </row>
     <row r="111" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A111" s="18" t="s">
+      <c r="A111" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="11" t="s">
         <v>234</v>
       </c>
       <c r="C111" s="8" t="s">
@@ -3355,10 +3412,12 @@
       </c>
     </row>
     <row r="112" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="18" t="s">
+      <c r="A112" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="B112" s="12"/>
+      <c r="B112" s="11" t="s">
+        <v>234</v>
+      </c>
       <c r="C112" s="8" t="s">
         <v>236</v>
       </c>
@@ -3370,10 +3429,12 @@
       </c>
     </row>
     <row r="113" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="18" t="s">
+      <c r="A113" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="B113" s="12"/>
+      <c r="B113" s="11" t="s">
+        <v>234</v>
+      </c>
       <c r="C113" s="8" t="s">
         <v>66</v>
       </c>
@@ -3386,13 +3447,13 @@
       </c>
     </row>
     <row r="114" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="19" t="s">
+      <c r="A114" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="C114" s="12" t="s">
+      <c r="C114" s="11" t="s">
         <v>240</v>
       </c>
       <c r="D114" s="8" t="s">
@@ -3403,9 +3464,15 @@
       </c>
     </row>
     <row r="115" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A115" s="19"/>
-      <c r="B115" s="12"/>
-      <c r="C115" s="12"/>
+      <c r="A115" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>240</v>
+      </c>
       <c r="D115" s="8" t="s">
         <v>54</v>
       </c>
@@ -3415,13 +3482,13 @@
       </c>
     </row>
     <row r="116" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="19" t="s">
+      <c r="A116" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="B116" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="11" t="s">
         <v>243</v>
       </c>
       <c r="D116" s="8" t="s">
@@ -3433,9 +3500,15 @@
       </c>
     </row>
     <row r="117" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="19"/>
-      <c r="B117" s="12"/>
-      <c r="C117" s="12"/>
+      <c r="A117" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>243</v>
+      </c>
       <c r="D117" s="8" t="s">
         <v>24</v>
       </c>
@@ -3444,7 +3517,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="18" t="s">
+      <c r="A118" s="17" t="s">
         <v>244</v>
       </c>
       <c r="B118" s="8" t="s">
@@ -3462,7 +3535,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="18"/>
+      <c r="A119" s="17"/>
       <c r="B119" s="8" t="s">
         <v>245</v>
       </c>
@@ -3477,7 +3550,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="18" t="s">
+      <c r="A120" s="17" t="s">
         <v>248</v>
       </c>
       <c r="B120" s="8" t="s">
@@ -3494,7 +3567,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="18" t="s">
+      <c r="A121" s="17" t="s">
         <v>251</v>
       </c>
       <c r="B121" s="8" t="s">
@@ -3546,13 +3619,13 @@
       </c>
     </row>
     <row r="124" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="12" t="s">
+      <c r="A124" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B124" s="12" t="s">
+      <c r="B124" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="C124" s="12" t="s">
+      <c r="C124" s="11" t="s">
         <v>232</v>
       </c>
       <c r="D124" s="8"/>
@@ -3561,10 +3634,16 @@
       </c>
     </row>
     <row r="125" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="12"/>
-      <c r="B125" s="12"/>
-      <c r="C125" s="12"/>
-      <c r="D125" s="20" t="s">
+      <c r="A125" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B125" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D125" s="18" t="s">
         <v>137</v>
       </c>
       <c r="E125" s="10">
@@ -3572,9 +3651,15 @@
       </c>
     </row>
     <row r="126" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="12"/>
-      <c r="B126" s="12"/>
-      <c r="C126" s="12"/>
+      <c r="A126" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>232</v>
+      </c>
       <c r="D126" s="8" t="s">
         <v>66</v>
       </c>
@@ -3602,7 +3687,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="18" t="s">
+      <c r="A128" s="17" t="s">
         <v>260</v>
       </c>
       <c r="B128" s="8" t="s">
@@ -3620,7 +3705,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="18" t="s">
+      <c r="A129" s="17" t="s">
         <v>263</v>
       </c>
       <c r="B129" s="8" t="s">
@@ -3635,10 +3720,10 @@
       <c r="E129" s="9"/>
     </row>
     <row r="130" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="12" t="s">
+      <c r="A130" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B130" s="12" t="s">
+      <c r="B130" s="11" t="s">
         <v>266</v>
       </c>
       <c r="C130" s="8" t="s">
@@ -3652,8 +3737,12 @@
       </c>
     </row>
     <row r="131" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="12"/>
-      <c r="B131" s="12"/>
+      <c r="A131" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B131" s="11" t="s">
+        <v>266</v>
+      </c>
       <c r="C131" s="8" t="s">
         <v>267</v>
       </c>
@@ -3692,12 +3781,12 @@
       <c r="D133" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E133" s="21">
+      <c r="E133" s="19">
         <v>3.6857142857142855</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="18" t="s">
+      <c r="A134" s="17" t="s">
         <v>269</v>
       </c>
       <c r="B134" s="8" t="s">
@@ -3715,7 +3804,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="18"/>
+      <c r="A135" s="17"/>
       <c r="B135" s="8" t="s">
         <v>270</v>
       </c>
@@ -3764,16 +3853,16 @@
       </c>
     </row>
     <row r="138" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="12" t="s">
+      <c r="A138" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B138" s="19" t="s">
+      <c r="B138" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="C138" s="19" t="s">
+      <c r="C138" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="D138" s="18" t="s">
+      <c r="D138" s="17" t="s">
         <v>54</v>
       </c>
       <c r="E138" s="9">
@@ -3781,10 +3870,16 @@
       </c>
     </row>
     <row r="139" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="12"/>
-      <c r="B139" s="19"/>
-      <c r="C139" s="19"/>
-      <c r="D139" s="18" t="s">
+      <c r="A139" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C139" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="D139" s="17" t="s">
         <v>137</v>
       </c>
       <c r="E139" s="9">
@@ -3793,14 +3888,16 @@
       </c>
     </row>
     <row r="140" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="12" t="s">
+      <c r="A140" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="B140" s="19"/>
-      <c r="C140" s="19" t="s">
+      <c r="B140" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C140" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="D140" s="18" t="s">
+      <c r="D140" s="17" t="s">
         <v>49</v>
       </c>
       <c r="E140" s="9">
@@ -3808,10 +3905,16 @@
       </c>
     </row>
     <row r="141" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="12"/>
-      <c r="B141" s="19"/>
-      <c r="C141" s="19"/>
-      <c r="D141" s="18" t="s">
+      <c r="A141" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="B141" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C141" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D141" s="17" t="s">
         <v>54</v>
       </c>
       <c r="E141" s="10">
@@ -3819,10 +3922,16 @@
       </c>
     </row>
     <row r="142" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="12"/>
-      <c r="B142" s="19"/>
-      <c r="C142" s="19"/>
-      <c r="D142" s="18" t="s">
+      <c r="A142" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="B142" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C142" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D142" s="17" t="s">
         <v>24</v>
       </c>
       <c r="E142" s="9">
@@ -3833,13 +3942,13 @@
       <c r="A143" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="B143" s="18" t="s">
+      <c r="B143" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="C143" s="18" t="s">
+      <c r="C143" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="D143" s="18" t="s">
+      <c r="D143" s="17" t="s">
         <v>137</v>
       </c>
       <c r="E143" s="10">
@@ -3848,16 +3957,16 @@
       </c>
     </row>
     <row r="144" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="13" t="s">
+      <c r="A144" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="B144" s="22" t="s">
+      <c r="B144" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C144" s="18" t="s">
+      <c r="C144" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="D144" s="18" t="s">
+      <c r="D144" s="17" t="s">
         <v>54</v>
       </c>
       <c r="E144" s="9">
@@ -3865,16 +3974,16 @@
       </c>
     </row>
     <row r="145" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="13" t="s">
+      <c r="A145" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="B145" s="22" t="s">
+      <c r="B145" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C145" s="18" t="s">
+      <c r="C145" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="D145" s="18" t="s">
+      <c r="D145" s="17" t="s">
         <v>24</v>
       </c>
       <c r="E145" s="9">
@@ -3882,22 +3991,22 @@
       </c>
     </row>
     <row r="146" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="13" t="s">
+      <c r="A146" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B146" s="22" t="s">
+      <c r="B146" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="C146" s="18" t="s">
+      <c r="C146" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="D146" s="18" t="s">
+      <c r="D146" s="17" t="s">
         <v>232</v>
       </c>
       <c r="E146" s="9"/>
     </row>
     <row r="147" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="18" t="s">
+      <c r="A147" s="17" t="s">
         <v>286</v>
       </c>
       <c r="B147" s="8" t="s">
@@ -3915,16 +4024,16 @@
       </c>
     </row>
     <row r="148" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="12" t="s">
+      <c r="A148" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="B148" s="19" t="s">
+      <c r="B148" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="C148" s="19" t="s">
+      <c r="C148" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="D148" s="18" t="s">
+      <c r="D148" s="17" t="s">
         <v>54</v>
       </c>
       <c r="E148" s="9">
@@ -3932,10 +4041,16 @@
       </c>
     </row>
     <row r="149" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="12"/>
-      <c r="B149" s="19"/>
-      <c r="C149" s="19"/>
-      <c r="D149" s="18" t="s">
+      <c r="A149" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="B149" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C149" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="D149" s="17" t="s">
         <v>137</v>
       </c>
       <c r="E149" s="10">
@@ -3961,16 +4076,16 @@
       </c>
     </row>
     <row r="151" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="12" t="s">
+      <c r="A151" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="B151" s="12" t="s">
+      <c r="B151" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="C151" s="12" t="s">
+      <c r="C151" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D151" s="12" t="s">
+      <c r="D151" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E151" s="10">
@@ -3978,123 +4093,125 @@
       </c>
     </row>
     <row r="152" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="12"/>
-      <c r="B152" s="12"/>
-      <c r="C152" s="12"/>
-      <c r="D152" s="12"/>
-      <c r="E152" s="9"/>
+      <c r="A152" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B152" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="C152" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="D152" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="E152" s="9">
+        <v>1.39</v>
+      </c>
     </row>
     <row r="153" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="B153" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="C153" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="D153" s="18" t="s">
-        <v>297</v>
+      <c r="A153" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B153" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="E153" s="9">
-        <v>1.39</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B154" s="12" t="s">
+      <c r="A154" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="B154" s="11" t="s">
         <v>299</v>
       </c>
       <c r="C154" s="8" t="s">
-        <v>293</v>
+        <v>69</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E154" s="9">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="B155" s="12"/>
-      <c r="C155" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D155" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E155" s="9">
         <f>12.42/33.88</f>
         <v>0.36658795749704837</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" s="18" t="s">
+    <row r="155" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A155" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B155" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="C156" s="8" t="s">
+      <c r="C155" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D156" s="8" t="s">
+      <c r="D155" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E156" s="10">
+      <c r="E155" s="10">
         <f>25/76</f>
         <v>0.32894736842105265</v>
       </c>
     </row>
+    <row r="156" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A156" s="17"/>
+      <c r="B156" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D156" s="8"/>
+      <c r="E156" s="9">
+        <v>0</v>
+      </c>
+    </row>
     <row r="157" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="18"/>
+      <c r="A157" s="17"/>
       <c r="B157" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C157" s="8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D157" s="8"/>
-      <c r="E157" s="9">
-        <v>0</v>
+      <c r="E157" s="10">
+        <v>0.94</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="18"/>
+      <c r="A158" s="17" t="s">
+        <v>303</v>
+      </c>
       <c r="B158" s="8" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C158" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D158" s="8"/>
+        <v>305</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="E158" s="10">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="B159" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="C159" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="D159" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E159" s="10">
         <f>27.09/36.8</f>
         <v>0.7361413043478261</v>
       </c>
+    </row>
+    <row r="159" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="3"/>
     </row>
     <row r="160" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
@@ -4328,7 +4445,7 @@
       <c r="E192" s="3"/>
     </row>
     <row r="193" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A193" s="2"/>
+      <c r="A193" s="4"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
@@ -4398,21 +4515,21 @@
       <c r="E202" s="3"/>
     </row>
     <row r="203" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A203" s="4"/>
+      <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
       <c r="E203" s="3"/>
     </row>
     <row r="204" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
+      <c r="A204" s="4"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
       <c r="E204" s="3"/>
     </row>
     <row r="205" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A205" s="4"/>
+      <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
       <c r="D205" s="2"/>
@@ -4426,38 +4543,38 @@
       <c r="E206" s="3"/>
     </row>
     <row r="207" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A207" s="2"/>
+      <c r="A207" s="4"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
       <c r="E207" s="3"/>
     </row>
     <row r="208" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A208" s="4"/>
-      <c r="B208" s="2"/>
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
+      <c r="A208" s="2"/>
+      <c r="B208" s="4"/>
+      <c r="C208" s="4"/>
+      <c r="D208" s="4"/>
       <c r="E208" s="3"/>
     </row>
     <row r="209" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="2"/>
-      <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="4"/>
+      <c r="B209" s="2"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="2"/>
       <c r="E209" s="3"/>
     </row>
     <row r="210" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="2"/>
-      <c r="B210" s="2"/>
-      <c r="C210" s="2"/>
-      <c r="D210" s="2"/>
+      <c r="B210" s="4"/>
+      <c r="C210" s="4"/>
+      <c r="D210" s="4"/>
       <c r="E210" s="3"/>
     </row>
     <row r="211" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A211" s="2"/>
-      <c r="B211" s="4"/>
-      <c r="C211" s="4"/>
-      <c r="D211" s="4"/>
+      <c r="A211" s="4"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
       <c r="E211" s="3"/>
     </row>
     <row r="212" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -4468,17 +4585,17 @@
       <c r="E212" s="3"/>
     </row>
     <row r="213" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A213" s="4"/>
+      <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
       <c r="E213" s="3"/>
     </row>
-    <row r="214" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A214" s="2"/>
-      <c r="B214" s="2"/>
-      <c r="C214" s="2"/>
-      <c r="D214" s="2"/>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+      <c r="C214" s="1"/>
+      <c r="D214" s="1"/>
       <c r="E214" s="3"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -10130,64 +10247,12 @@
       <c r="D1021" s="1"/>
       <c r="E1021" s="3"/>
     </row>
-    <row r="1022" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1022" s="1"/>
-      <c r="B1022" s="1"/>
-      <c r="C1022" s="1"/>
-      <c r="D1022" s="1"/>
-      <c r="E1022" s="3"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{CA673556-6469-4516-B6CA-C76DCD1ABD75}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E155">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
-  <mergeCells count="43">
-    <mergeCell ref="D151:D152"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A148:A149"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="C151:C152"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="A138:A139"/>
-    <mergeCell ref="B138:B142"/>
-    <mergeCell ref="C138:C139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="C140:C142"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="C116:C117"/>
-    <mergeCell ref="A124:A126"/>
-    <mergeCell ref="B124:B126"/>
-    <mergeCell ref="C124:C126"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="A109:A110"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="B93:B95"/>
-    <mergeCell ref="A105:A106"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B46"/>
-  </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
